--- a/output/pdf_financials_xlsx/MENE.xlsx
+++ b/output/pdf_financials_xlsx/MENE.xlsx
@@ -6423,19 +6423,19 @@
         <v>2.654995</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.654995</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.698095</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.698095</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.698095</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.698095</v>
       </c>
       <c r="K92" s="3" t="n">
         <v>2.005119</v>
@@ -8064,13 +8064,13 @@
         <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>2.631484</v>
+        <v>1.616791</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>3.626722</v>
+        <v>3.615946</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>5.619879</v>
+        <v>5.608679</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>2.056516</v>
@@ -21308,7 +21308,11 @@
           <t>Share-Based Payments Reserve</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -22256,7 +22260,11 @@
           <t>Share-Based Payments Reserve</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -22790,7 +22798,11 @@
           <t>Share-Based Payments Reserve</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -23728,7 +23740,11 @@
           <t>Share-Based Payments Reserve</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
@@ -24240,7 +24256,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -39166,7 +39186,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E287" t="inlineStr">
         <is>
           <t>-</t>
@@ -58585,7 +58609,7 @@
         <v>-0.122225</v>
       </c>
       <c r="N472" s="5" t="n">
-        <v>0.09690799999999999</v>
+        <v>-0.09690799999999999</v>
       </c>
       <c r="O472" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MENE.xlsx
+++ b/output/pdf_financials_xlsx/MENE.xlsx
@@ -1077,13 +1077,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.009213000000000001</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>2.9e-05</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1107,25 +1107,25 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.12672</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.413227</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.222692</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.027745</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.159878</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.378368</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.308233</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>0</v>
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-4.292341</v>
+        <v>-4.301554</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-1.833407</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-5.842961</v>
+        <v>-5.84299</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-3.165811</v>
@@ -2120,25 +2120,25 @@
         <v>-1.366768</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-6.970662</v>
+        <v>-7.097382</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-6.764622</v>
+        <v>-7.177849</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-3.344932</v>
+        <v>-3.567624</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.215631</v>
+        <v>-0.243376</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-1.281447</v>
+        <v>-1.441325</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-1.987738</v>
+        <v>-2.366106</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.993933</v>
+        <v>-1.302166</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>1.050832</v>
@@ -2212,13 +2212,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-4.292341</v>
+        <v>-4.301554</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-1.833407</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-5.842961</v>
+        <v>-5.84299</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-3.165811</v>
@@ -2242,25 +2242,25 @@
         <v>-1.311197</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-6.806896</v>
+        <v>-6.933616</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-6.607235</v>
+        <v>-7.020462</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-3.171769</v>
+        <v>-3.394461</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.044792</v>
+        <v>-0.072537</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-1.101969</v>
+        <v>-1.261847</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.771576</v>
+        <v>-2.149944</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.782473</v>
+        <v>-1.090706</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>1.050832</v>
@@ -2321,25 +2321,25 @@
         <v>-2051.662520145832</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-88.58314130482735</v>
+        <v>-90.23224181497879</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-50.58205960187433</v>
+        <v>-53.74554216956015</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-15.01106507761172</v>
+        <v>-16.06500188835157</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-0.1673012613070377</v>
+        <v>-0.2709307820911903</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-4.094762150238672</v>
+        <v>-4.688846360462243</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-7.606642789602717</v>
+        <v>-9.231247220356126</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-3.032866241603709</v>
+        <v>-4.227577701613495</v>
       </c>
       <c r="S30" s="1" t="inlineStr">
         <is>
@@ -2508,28 +2508,28 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.253627</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.001151</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.010378</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.020883</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>7e-06</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.003273</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.000234</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.000147</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>9.193095</v>
@@ -2550,10 +2550,10 @@
         <v>1.056528</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>8.094511000000001</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>7.39412</v>
       </c>
       <c r="S34" s="1" t="inlineStr">
         <is>
@@ -2638,28 +2638,28 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.253627</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.001151</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.010378</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.020883</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>7e-06</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.003273</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.000234</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.000147</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>9.269548</v>
@@ -2680,10 +2680,10 @@
         <v>12.965912</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.165486</v>
+        <v>8.259997</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.178279</v>
+        <v>7.572399</v>
       </c>
       <c r="S36" s="1" t="inlineStr">
         <is>
@@ -3418,25 +3418,25 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.270748</v>
+        <v>0.017121</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>12.894209</v>
+        <v>12.893058</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>11.472069</v>
+        <v>11.461691</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>7.88671</v>
+        <v>7.865827</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.261479</v>
+        <v>2.261472</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.236934</v>
+        <v>0.233661</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.00111</v>
+        <v>0.000876</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0</v>
@@ -3460,10 +3460,10 @@
         <v>0.551237</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>8.311286000000001</v>
+        <v>0.216775</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>7.44414</v>
+        <v>0.05002</v>
       </c>
       <c r="S48" s="1" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -20400,7 +20400,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -47034,7 +47034,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -51596,7 +51596,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -55166,7 +55166,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -66518,7 +66518,7 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E548" s="5" t="n">
